--- a/estandar-a/templates/4-4-1-reporte-evaluacion-resultados.xlsx
+++ b/estandar-a/templates/4-4-1-reporte-evaluacion-resultados.xlsx
@@ -13,7 +13,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tabla antes después de indicado" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registro de incidencias" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Tabla 1'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Referencia de trabajo del F21'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Tu turno · preguntas guía'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Tabla antes después de indicado'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Registro de incidencias'!$1:$1</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -30,17 +36,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Afacad"/>
+      <name val="Calibri"/>
       <color rgb="004B5563"/>
-      <sz val="10"/>
+      <sz val="10.5"/>
     </font>
     <font>
-      <name val="Afacad"/>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10.5"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -52,8 +59,13 @@
         <fgColor rgb="0028467E"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3F6FB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -61,16 +73,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9D3E4"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C9D3E4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C9D3E4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9D3E4"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -446,7 +475,7 @@
     <col width="42" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Mi CompañIA</t>
@@ -483,7 +512,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>MiPyME</t>
@@ -530,7 +559,7 @@
     <col width="42" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>#</t>
@@ -561,17 +590,17 @@
       <c r="C2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Tablero de indicadores integrado Visualización gráfica (puedes generar gráficas con Excel mismo) con resultados cuantitativos + cualitativos.</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -587,17 +616,17 @@
       <c r="C4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Cálculo del ROI Beneficios obtenidos / costo total del proyecto × 100. Documenta los supuestos.</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -613,17 +642,17 @@
       <c r="C6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Nivel de adopción del personal ¿Cuántas personas operan cada solución activamente? ¿Qué porcentaje del personal capacitado la usa? Evidencia: logs, encuesta a usuarios.</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -660,7 +689,7 @@
     <col width="13" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>#</t>
@@ -708,19 +737,19 @@
       <c r="F2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2">
+      <c r="B3" s="3" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3">
         <f>(actual-base)/base</f>
         <v/>
       </c>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -738,19 +767,19 @@
       <c r="F4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr"/>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="2">
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3">
         <f>(actual-base)/base</f>
         <v/>
       </c>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -768,19 +797,19 @@
       <c r="F6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr"/>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="2">
+      <c r="B7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3">
         <f>(actual-base)/base</f>
         <v/>
       </c>
-      <c r="F7" s="2" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -803,7 +832,7 @@
     <col width="19" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>#</t>
@@ -842,15 +871,15 @@
       <c r="E2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -864,15 +893,15 @@
       <c r="E4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr"/>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr"/>
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
